--- a/data_assets/mapping/dws_to_ads/ADS应用层数据模型_CRM_ V1.0.xlsx
+++ b/data_assets/mapping/dws_to_ads/ADS应用层数据模型_CRM_ V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="726" firstSheet="15" activeTab="23"/>
+    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="726" firstSheet="16" activeTab="23"/>
   </bookViews>
   <sheets>
     <sheet name="修订记录" sheetId="1" r:id="rId1"/>
@@ -18097,7 +18097,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:Q284"/>
   <sheetFormatPr defaultColWidth="8.23148148148148" defaultRowHeight="14.4"/>
   <cols>
@@ -18287,7 +18287,7 @@
       <c r="P7" s="33"/>
       <c r="Q7" s="33"/>
     </row>
-    <row r="8" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
       <c r="B8" s="25" t="s">
         <v>192</v>
@@ -18314,7 +18314,7 @@
       <c r="P8" s="33"/>
       <c r="Q8" s="33"/>
     </row>
-    <row r="9" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
       <c r="B9" s="25" t="s">
         <v>64</v>
@@ -18341,7 +18341,7 @@
       <c r="P9" s="33"/>
       <c r="Q9" s="33"/>
     </row>
-    <row r="10" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="24"/>
       <c r="B10" s="25" t="s">
         <v>66</v>
@@ -18368,7 +18368,7 @@
       <c r="P10" s="33"/>
       <c r="Q10" s="33"/>
     </row>
-    <row r="11" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="24"/>
       <c r="B11" s="25" t="s">
         <v>62</v>
@@ -18395,7 +18395,7 @@
       <c r="P11" s="33"/>
       <c r="Q11" s="33"/>
     </row>
-    <row r="12" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="24"/>
       <c r="B12" s="25" t="s">
         <v>611</v>
@@ -18422,7 +18422,7 @@
       <c r="P12" s="33"/>
       <c r="Q12" s="33"/>
     </row>
-    <row r="13" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="24"/>
       <c r="B13" s="25" t="s">
         <v>613</v>
@@ -18449,7 +18449,7 @@
       <c r="P13" s="33"/>
       <c r="Q13" s="33"/>
     </row>
-    <row r="14" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="14" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="24"/>
       <c r="B14" s="25" t="s">
         <v>615</v>
@@ -18476,7 +18476,7 @@
       <c r="P14" s="33"/>
       <c r="Q14" s="33"/>
     </row>
-    <row r="15" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="15" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="24"/>
       <c r="B15" s="25" t="s">
         <v>593</v>
@@ -18503,7 +18503,7 @@
       <c r="P15" s="33"/>
       <c r="Q15" s="33"/>
     </row>
-    <row r="16" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="24"/>
       <c r="B16" s="25" t="s">
         <v>618</v>
@@ -18530,7 +18530,7 @@
       <c r="P16" s="33"/>
       <c r="Q16" s="33"/>
     </row>
-    <row r="17" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="24"/>
       <c r="B17" s="25" t="s">
         <v>620</v>
@@ -18557,7 +18557,7 @@
       <c r="P17" s="33"/>
       <c r="Q17" s="33"/>
     </row>
-    <row r="18" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="24"/>
       <c r="B18" s="25" t="s">
         <v>103</v>
@@ -18584,7 +18584,7 @@
       <c r="P18" s="33"/>
       <c r="Q18" s="33"/>
     </row>
-    <row r="19" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A19" s="24"/>
       <c r="B19" s="25" t="s">
         <v>622</v>
@@ -18611,7 +18611,7 @@
       <c r="P19" s="33"/>
       <c r="Q19" s="33"/>
     </row>
-    <row r="20" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A20" s="24"/>
       <c r="B20" s="25" t="s">
         <v>624</v>
@@ -18638,7 +18638,7 @@
       <c r="P20" s="33"/>
       <c r="Q20" s="33"/>
     </row>
-    <row r="21" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A21" s="24"/>
       <c r="B21" s="25" t="s">
         <v>626</v>
@@ -18665,7 +18665,7 @@
       <c r="P21" s="33"/>
       <c r="Q21" s="33"/>
     </row>
-    <row r="22" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A22" s="24"/>
       <c r="B22" s="25" t="s">
         <v>628</v>
@@ -18692,7 +18692,7 @@
       <c r="P22" s="33"/>
       <c r="Q22" s="33"/>
     </row>
-    <row r="23" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="23" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A23" s="24"/>
       <c r="B23" s="25" t="s">
         <v>630</v>
@@ -18719,7 +18719,7 @@
       <c r="P23" s="33"/>
       <c r="Q23" s="33"/>
     </row>
-    <row r="24" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="24" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A24" s="24"/>
       <c r="B24" s="25" t="s">
         <v>632</v>
@@ -18746,7 +18746,7 @@
       <c r="P24" s="33"/>
       <c r="Q24" s="33"/>
     </row>
-    <row r="25" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="25" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A25" s="24"/>
       <c r="B25" s="25" t="s">
         <v>634</v>
@@ -18773,7 +18773,7 @@
       <c r="P25" s="33"/>
       <c r="Q25" s="33"/>
     </row>
-    <row r="26" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="26" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A26" s="24"/>
       <c r="B26" s="25" t="s">
         <v>636</v>
@@ -18800,7 +18800,7 @@
       <c r="P26" s="33"/>
       <c r="Q26" s="33"/>
     </row>
-    <row r="27" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="27" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A27" s="24"/>
       <c r="B27" s="25" t="s">
         <v>638</v>
@@ -18827,7 +18827,7 @@
       <c r="P27" s="33"/>
       <c r="Q27" s="33"/>
     </row>
-    <row r="28" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="28" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A28" s="24"/>
       <c r="B28" s="36" t="s">
         <v>640</v>
@@ -18854,7 +18854,7 @@
       <c r="P28" s="33"/>
       <c r="Q28" s="33"/>
     </row>
-    <row r="29" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="29" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A29" s="24"/>
       <c r="B29" s="36" t="s">
         <v>642</v>
@@ -18881,7 +18881,7 @@
       <c r="P29" s="33"/>
       <c r="Q29" s="33"/>
     </row>
-    <row r="30" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="30" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A30" s="24"/>
       <c r="B30" s="36" t="s">
         <v>644</v>
@@ -18908,7 +18908,7 @@
       <c r="P30" s="33"/>
       <c r="Q30" s="33"/>
     </row>
-    <row r="31" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="31" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A31" s="24"/>
       <c r="B31" s="36" t="s">
         <v>646</v>
@@ -18935,7 +18935,7 @@
       <c r="P31" s="33"/>
       <c r="Q31" s="33"/>
     </row>
-    <row r="32" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="32" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A32" s="24"/>
       <c r="B32" s="36" t="s">
         <v>648</v>
@@ -18962,7 +18962,7 @@
       <c r="P32" s="33"/>
       <c r="Q32" s="33"/>
     </row>
-    <row r="33" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="33" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A33" s="24"/>
       <c r="B33" s="36" t="s">
         <v>650</v>
@@ -18989,7 +18989,7 @@
       <c r="P33" s="33"/>
       <c r="Q33" s="33"/>
     </row>
-    <row r="34" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="34" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A34" s="24"/>
       <c r="B34" s="36" t="s">
         <v>652</v>
@@ -19016,7 +19016,7 @@
       <c r="P34" s="33"/>
       <c r="Q34" s="33"/>
     </row>
-    <row r="35" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="35" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A35" s="24"/>
       <c r="B35" s="36" t="s">
         <v>654</v>
@@ -19043,7 +19043,7 @@
       <c r="P35" s="33"/>
       <c r="Q35" s="33"/>
     </row>
-    <row r="36" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="36" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A36" s="24"/>
       <c r="B36" s="36" t="s">
         <v>656</v>
@@ -19070,7 +19070,7 @@
       <c r="P36" s="33"/>
       <c r="Q36" s="33"/>
     </row>
-    <row r="37" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="37" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A37" s="24"/>
       <c r="B37" s="36" t="s">
         <v>658</v>
@@ -19097,7 +19097,7 @@
       <c r="P37" s="33"/>
       <c r="Q37" s="33"/>
     </row>
-    <row r="38" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="38" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A38" s="24"/>
       <c r="B38" s="36" t="s">
         <v>269</v>
@@ -19124,7 +19124,7 @@
       <c r="P38" s="33"/>
       <c r="Q38" s="33"/>
     </row>
-    <row r="39" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="39" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A39" s="24"/>
       <c r="B39" s="36" t="s">
         <v>660</v>
@@ -19151,7 +19151,7 @@
       <c r="P39" s="33"/>
       <c r="Q39" s="33"/>
     </row>
-    <row r="40" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="40" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A40" s="24"/>
       <c r="B40" s="36" t="s">
         <v>662</v>
@@ -19178,7 +19178,7 @@
       <c r="P40" s="33"/>
       <c r="Q40" s="33"/>
     </row>
-    <row r="41" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="41" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A41" s="24"/>
       <c r="B41" s="36" t="s">
         <v>273</v>
@@ -19205,7 +19205,7 @@
       <c r="P41" s="33"/>
       <c r="Q41" s="33"/>
     </row>
-    <row r="42" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="42" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A42" s="24"/>
       <c r="B42" s="36" t="s">
         <v>663</v>
@@ -19232,7 +19232,7 @@
       <c r="P42" s="33"/>
       <c r="Q42" s="33"/>
     </row>
-    <row r="43" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="43" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A43" s="24"/>
       <c r="B43" s="36" t="s">
         <v>665</v>
@@ -19259,7 +19259,7 @@
       <c r="P43" s="33"/>
       <c r="Q43" s="33"/>
     </row>
-    <row r="44" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="44" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A44" s="24"/>
       <c r="B44" s="36" t="s">
         <v>667</v>
@@ -19286,7 +19286,7 @@
       <c r="P44" s="33"/>
       <c r="Q44" s="33"/>
     </row>
-    <row r="45" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="45" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A45" s="24"/>
       <c r="B45" s="36" t="s">
         <v>670</v>
@@ -19313,7 +19313,7 @@
       <c r="P45" s="33"/>
       <c r="Q45" s="33"/>
     </row>
-    <row r="46" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="46" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A46" s="24"/>
       <c r="B46" s="36" t="s">
         <v>672</v>
@@ -19340,7 +19340,7 @@
       <c r="P46" s="33"/>
       <c r="Q46" s="33"/>
     </row>
-    <row r="47" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="47" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A47" s="24"/>
       <c r="B47" s="36" t="s">
         <v>674</v>
@@ -19367,7 +19367,7 @@
       <c r="P47" s="33"/>
       <c r="Q47" s="33"/>
     </row>
-    <row r="48" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="48" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A48" s="24"/>
       <c r="B48" s="36" t="s">
         <v>676</v>
@@ -19394,7 +19394,7 @@
       <c r="P48" s="33"/>
       <c r="Q48" s="33"/>
     </row>
-    <row r="49" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="49" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A49" s="24"/>
       <c r="B49" s="36" t="s">
         <v>283</v>
@@ -19421,7 +19421,7 @@
       <c r="P49" s="33"/>
       <c r="Q49" s="33"/>
     </row>
-    <row r="50" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="50" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A50" s="24"/>
       <c r="B50" s="36" t="s">
         <v>679</v>
@@ -19448,7 +19448,7 @@
       <c r="P50" s="33"/>
       <c r="Q50" s="33"/>
     </row>
-    <row r="51" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="51" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A51" s="24"/>
       <c r="B51" s="36" t="s">
         <v>681</v>
@@ -19475,7 +19475,7 @@
       <c r="P51" s="33"/>
       <c r="Q51" s="33"/>
     </row>
-    <row r="52" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="52" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A52" s="24"/>
       <c r="B52" s="36" t="s">
         <v>683</v>
@@ -19502,7 +19502,7 @@
       <c r="P52" s="33"/>
       <c r="Q52" s="33"/>
     </row>
-    <row r="53" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="53" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A53" s="24"/>
       <c r="B53" s="36" t="s">
         <v>685</v>
@@ -19529,7 +19529,7 @@
       <c r="P53" s="33"/>
       <c r="Q53" s="33"/>
     </row>
-    <row r="54" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="54" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A54" s="24"/>
       <c r="B54" s="36" t="s">
         <v>687</v>
@@ -19556,7 +19556,7 @@
       <c r="P54" s="33"/>
       <c r="Q54" s="33"/>
     </row>
-    <row r="55" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="55" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A55" s="24"/>
       <c r="B55" s="36" t="s">
         <v>689</v>
@@ -19583,7 +19583,7 @@
       <c r="P55" s="33"/>
       <c r="Q55" s="33"/>
     </row>
-    <row r="56" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="56" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A56" s="24"/>
       <c r="B56" s="36" t="s">
         <v>691</v>
@@ -19610,7 +19610,7 @@
       <c r="P56" s="33"/>
       <c r="Q56" s="33"/>
     </row>
-    <row r="57" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="57" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A57" s="24"/>
       <c r="B57" s="36" t="s">
         <v>693</v>
@@ -19637,7 +19637,7 @@
       <c r="P57" s="33"/>
       <c r="Q57" s="33"/>
     </row>
-    <row r="58" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="58" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A58" s="24"/>
       <c r="B58" s="36" t="s">
         <v>695</v>
@@ -19664,7 +19664,7 @@
       <c r="P58" s="33"/>
       <c r="Q58" s="33"/>
     </row>
-    <row r="59" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="59" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A59" s="24"/>
       <c r="B59" s="36" t="s">
         <v>697</v>
@@ -19691,7 +19691,7 @@
       <c r="P59" s="33"/>
       <c r="Q59" s="33"/>
     </row>
-    <row r="60" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="60" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A60" s="24"/>
       <c r="B60" s="36" t="s">
         <v>699</v>
@@ -19718,7 +19718,7 @@
       <c r="P60" s="33"/>
       <c r="Q60" s="33"/>
     </row>
-    <row r="61" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="61" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A61" s="24"/>
       <c r="B61" s="36" t="s">
         <v>701</v>
@@ -19745,7 +19745,7 @@
       <c r="P61" s="33"/>
       <c r="Q61" s="33"/>
     </row>
-    <row r="62" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="62" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A62" s="24"/>
       <c r="B62" s="36" t="s">
         <v>277</v>
@@ -19772,7 +19772,7 @@
       <c r="P62" s="33"/>
       <c r="Q62" s="33"/>
     </row>
-    <row r="63" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="63" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A63" s="24"/>
       <c r="B63" s="36" t="s">
         <v>704</v>
@@ -19799,7 +19799,7 @@
       <c r="P63" s="33"/>
       <c r="Q63" s="33"/>
     </row>
-    <row r="64" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="64" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A64" s="24"/>
       <c r="B64" s="36" t="s">
         <v>706</v>
@@ -19826,7 +19826,7 @@
       <c r="P64" s="33"/>
       <c r="Q64" s="33"/>
     </row>
-    <row r="65" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="65" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A65" s="24"/>
       <c r="B65" s="36" t="s">
         <v>708</v>
@@ -19853,7 +19853,7 @@
       <c r="P65" s="33"/>
       <c r="Q65" s="33"/>
     </row>
-    <row r="66" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="66" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A66" s="24"/>
       <c r="B66" s="36" t="s">
         <v>710</v>
@@ -19880,7 +19880,7 @@
       <c r="P66" s="33"/>
       <c r="Q66" s="33"/>
     </row>
-    <row r="67" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="67" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A67" s="24"/>
       <c r="B67" s="36" t="s">
         <v>712</v>
@@ -19907,7 +19907,7 @@
       <c r="P67" s="33"/>
       <c r="Q67" s="33"/>
     </row>
-    <row r="68" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="68" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A68" s="24"/>
       <c r="B68" s="36" t="s">
         <v>279</v>
@@ -19934,7 +19934,7 @@
       <c r="P68" s="33"/>
       <c r="Q68" s="33"/>
     </row>
-    <row r="69" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="69" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A69" s="24"/>
       <c r="B69" s="36" t="s">
         <v>714</v>
@@ -19961,7 +19961,7 @@
       <c r="P69" s="33"/>
       <c r="Q69" s="33"/>
     </row>
-    <row r="70" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="70" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A70" s="24"/>
       <c r="B70" s="36" t="s">
         <v>716</v>
@@ -19988,7 +19988,7 @@
       <c r="P70" s="33"/>
       <c r="Q70" s="33"/>
     </row>
-    <row r="71" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="71" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A71" s="24"/>
       <c r="B71" s="36" t="s">
         <v>718</v>
@@ -20015,7 +20015,7 @@
       <c r="P71" s="33"/>
       <c r="Q71" s="33"/>
     </row>
-    <row r="72" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="72" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A72" s="24"/>
       <c r="B72" s="36" t="s">
         <v>720</v>
@@ -20042,7 +20042,7 @@
       <c r="P72" s="33"/>
       <c r="Q72" s="33"/>
     </row>
-    <row r="73" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="73" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A73" s="24"/>
       <c r="B73" s="36" t="s">
         <v>722</v>
@@ -20069,7 +20069,7 @@
       <c r="P73" s="33"/>
       <c r="Q73" s="33"/>
     </row>
-    <row r="74" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="74" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A74" s="24"/>
       <c r="B74" s="36" t="s">
         <v>724</v>
@@ -20096,7 +20096,7 @@
       <c r="P74" s="33"/>
       <c r="Q74" s="33"/>
     </row>
-    <row r="75" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="75" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A75" s="24"/>
       <c r="B75" s="36" t="s">
         <v>315</v>
@@ -20123,7 +20123,7 @@
       <c r="P75" s="33"/>
       <c r="Q75" s="33"/>
     </row>
-    <row r="76" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="76" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A76" s="24"/>
       <c r="B76" s="36" t="s">
         <v>726</v>
@@ -20150,7 +20150,7 @@
       <c r="P76" s="33"/>
       <c r="Q76" s="33"/>
     </row>
-    <row r="77" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="77" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A77" s="24"/>
       <c r="B77" s="36" t="s">
         <v>728</v>
@@ -20177,7 +20177,7 @@
       <c r="P77" s="33"/>
       <c r="Q77" s="33"/>
     </row>
-    <row r="78" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="78" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A78" s="24"/>
       <c r="B78" s="36" t="s">
         <v>730</v>
@@ -20204,7 +20204,7 @@
       <c r="P78" s="33"/>
       <c r="Q78" s="33"/>
     </row>
-    <row r="79" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="79" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A79" s="24"/>
       <c r="B79" s="36" t="s">
         <v>732</v>
@@ -20231,7 +20231,7 @@
       <c r="P79" s="33"/>
       <c r="Q79" s="33"/>
     </row>
-    <row r="80" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="80" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A80" s="24"/>
       <c r="B80" s="36" t="s">
         <v>734</v>
@@ -20258,7 +20258,7 @@
       <c r="P80" s="33"/>
       <c r="Q80" s="33"/>
     </row>
-    <row r="81" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="81" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A81" s="24"/>
       <c r="B81" s="36" t="s">
         <v>736</v>
@@ -20285,7 +20285,7 @@
       <c r="P81" s="33"/>
       <c r="Q81" s="33"/>
     </row>
-    <row r="82" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="82" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A82" s="24"/>
       <c r="B82" s="36" t="s">
         <v>738</v>
@@ -20312,7 +20312,7 @@
       <c r="P82" s="33"/>
       <c r="Q82" s="33"/>
     </row>
-    <row r="83" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="83" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A83" s="24"/>
       <c r="B83" s="36" t="s">
         <v>740</v>
@@ -20339,7 +20339,7 @@
       <c r="P83" s="33"/>
       <c r="Q83" s="33"/>
     </row>
-    <row r="84" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="84" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A84" s="24"/>
       <c r="B84" s="36" t="s">
         <v>742</v>
@@ -20366,7 +20366,7 @@
       <c r="P84" s="33"/>
       <c r="Q84" s="33"/>
     </row>
-    <row r="85" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="85" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A85" s="24"/>
       <c r="B85" s="36" t="s">
         <v>744</v>
@@ -20393,7 +20393,7 @@
       <c r="P85" s="33"/>
       <c r="Q85" s="33"/>
     </row>
-    <row r="86" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="86" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A86" s="24"/>
       <c r="B86" s="36" t="s">
         <v>746</v>
@@ -20420,7 +20420,7 @@
       <c r="P86" s="33"/>
       <c r="Q86" s="33"/>
     </row>
-    <row r="87" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="87" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A87" s="24"/>
       <c r="B87" s="36" t="s">
         <v>748</v>
@@ -20447,7 +20447,7 @@
       <c r="P87" s="33"/>
       <c r="Q87" s="33"/>
     </row>
-    <row r="88" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="88" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A88" s="24"/>
       <c r="B88" s="36" t="s">
         <v>750</v>
@@ -20474,7 +20474,7 @@
       <c r="P88" s="33"/>
       <c r="Q88" s="33"/>
     </row>
-    <row r="89" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="89" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A89" s="24"/>
       <c r="B89" s="36" t="s">
         <v>752</v>
@@ -20501,7 +20501,7 @@
       <c r="P89" s="33"/>
       <c r="Q89" s="33"/>
     </row>
-    <row r="90" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="90" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A90" s="24"/>
       <c r="B90" s="36" t="s">
         <v>754</v>
@@ -20528,7 +20528,7 @@
       <c r="P90" s="33"/>
       <c r="Q90" s="33"/>
     </row>
-    <row r="91" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="91" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A91" s="24"/>
       <c r="B91" s="36" t="s">
         <v>756</v>
@@ -20555,7 +20555,7 @@
       <c r="P91" s="33"/>
       <c r="Q91" s="33"/>
     </row>
-    <row r="92" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="92" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A92" s="24"/>
       <c r="B92" s="36" t="s">
         <v>758</v>
@@ -20582,7 +20582,7 @@
       <c r="P92" s="33"/>
       <c r="Q92" s="33"/>
     </row>
-    <row r="93" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="93" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A93" s="24"/>
       <c r="B93" s="36" t="s">
         <v>295</v>
@@ -20609,7 +20609,7 @@
       <c r="P93" s="33"/>
       <c r="Q93" s="33"/>
     </row>
-    <row r="94" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="94" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A94" s="24"/>
       <c r="B94" s="36" t="s">
         <v>760</v>
@@ -20636,7 +20636,7 @@
       <c r="P94" s="33"/>
       <c r="Q94" s="33"/>
     </row>
-    <row r="95" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="95" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A95" s="24"/>
       <c r="B95" s="36" t="s">
         <v>762</v>
@@ -20663,7 +20663,7 @@
       <c r="P95" s="33"/>
       <c r="Q95" s="33"/>
     </row>
-    <row r="96" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="96" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A96" s="24"/>
       <c r="B96" s="36" t="s">
         <v>764</v>
@@ -20690,7 +20690,7 @@
       <c r="P96" s="33"/>
       <c r="Q96" s="33"/>
     </row>
-    <row r="97" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="97" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A97" s="24"/>
       <c r="B97" s="36" t="s">
         <v>766</v>
@@ -20717,7 +20717,7 @@
       <c r="P97" s="33"/>
       <c r="Q97" s="33"/>
     </row>
-    <row r="98" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="98" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A98" s="24"/>
       <c r="B98" s="36" t="s">
         <v>769</v>
@@ -20744,7 +20744,7 @@
       <c r="P98" s="33"/>
       <c r="Q98" s="33"/>
     </row>
-    <row r="99" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="99" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A99" s="24"/>
       <c r="B99" s="36" t="s">
         <v>771</v>
@@ -20771,7 +20771,7 @@
       <c r="P99" s="33"/>
       <c r="Q99" s="33"/>
     </row>
-    <row r="100" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="100" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A100" s="24"/>
       <c r="B100" s="36" t="s">
         <v>773</v>
@@ -20798,7 +20798,7 @@
       <c r="P100" s="33"/>
       <c r="Q100" s="33"/>
     </row>
-    <row r="101" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="101" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A101" s="24"/>
       <c r="B101" s="36" t="s">
         <v>775</v>
@@ -20825,7 +20825,7 @@
       <c r="P101" s="33"/>
       <c r="Q101" s="33"/>
     </row>
-    <row r="102" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="102" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A102" s="24"/>
       <c r="B102" s="36" t="s">
         <v>777</v>
@@ -20852,7 +20852,7 @@
       <c r="P102" s="33"/>
       <c r="Q102" s="33"/>
     </row>
-    <row r="103" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="103" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A103" s="24"/>
       <c r="B103" s="36" t="s">
         <v>779</v>
@@ -20879,7 +20879,7 @@
       <c r="P103" s="33"/>
       <c r="Q103" s="33"/>
     </row>
-    <row r="104" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="104" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A104" s="24"/>
       <c r="B104" s="36" t="s">
         <v>781</v>
@@ -20906,7 +20906,7 @@
       <c r="P104" s="33"/>
       <c r="Q104" s="33"/>
     </row>
-    <row r="105" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="105" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A105" s="24"/>
       <c r="B105" s="36" t="s">
         <v>783</v>
@@ -20933,7 +20933,7 @@
       <c r="P105" s="33"/>
       <c r="Q105" s="33"/>
     </row>
-    <row r="106" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="106" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A106" s="24"/>
       <c r="B106" s="36" t="s">
         <v>785</v>
@@ -21022,7 +21022,7 @@
       <c r="P108" s="33"/>
       <c r="Q108" s="33"/>
     </row>
-    <row r="109" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="109" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A109" s="24"/>
       <c r="B109" s="40" t="s">
         <v>793</v>
@@ -21049,7 +21049,7 @@
       <c r="P109" s="33"/>
       <c r="Q109" s="33"/>
     </row>
-    <row r="110" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="110" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A110" s="24"/>
       <c r="B110" s="36" t="s">
         <v>795</v>
@@ -21076,7 +21076,7 @@
       <c r="P110" s="33"/>
       <c r="Q110" s="33"/>
     </row>
-    <row r="111" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="111" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A111" s="24"/>
       <c r="B111" s="36" t="s">
         <v>797</v>
@@ -21103,7 +21103,7 @@
       <c r="P111" s="33"/>
       <c r="Q111" s="33"/>
     </row>
-    <row r="112" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="112" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A112" s="24"/>
       <c r="B112" s="36" t="s">
         <v>799</v>
@@ -21192,7 +21192,7 @@
       <c r="P114" s="33"/>
       <c r="Q114" s="33"/>
     </row>
-    <row r="115" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="115" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A115" s="24"/>
       <c r="B115" s="36" t="s">
         <v>807</v>
@@ -21219,7 +21219,7 @@
       <c r="P115" s="33"/>
       <c r="Q115" s="33"/>
     </row>
-    <row r="116" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="116" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A116" s="24"/>
       <c r="B116" s="36" t="s">
         <v>809</v>
@@ -21304,7 +21304,7 @@
       <c r="P118" s="33"/>
       <c r="Q118" s="33"/>
     </row>
-    <row r="119" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="119" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A119" s="24"/>
       <c r="B119" s="36" t="s">
         <v>815</v>
@@ -21331,7 +21331,7 @@
       <c r="P119" s="33"/>
       <c r="Q119" s="33"/>
     </row>
-    <row r="120" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="120" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A120" s="24"/>
       <c r="B120" s="44" t="s">
         <v>817</v>
@@ -21389,7 +21389,7 @@
       <c r="P121" s="33"/>
       <c r="Q121" s="33"/>
     </row>
-    <row r="122" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="122" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A122" s="24"/>
       <c r="B122" s="43" t="s">
         <v>822</v>
@@ -21416,7 +21416,7 @@
       <c r="P122" s="33"/>
       <c r="Q122" s="33"/>
     </row>
-    <row r="123" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="123" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A123" s="24"/>
       <c r="B123" s="43" t="s">
         <v>824</v>
@@ -21443,7 +21443,7 @@
       <c r="P123" s="33"/>
       <c r="Q123" s="33"/>
     </row>
-    <row r="124" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="124" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A124" s="24"/>
       <c r="B124" s="43" t="s">
         <v>826</v>
@@ -21470,7 +21470,7 @@
       <c r="P124" s="33"/>
       <c r="Q124" s="33"/>
     </row>
-    <row r="125" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="125" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A125" s="24"/>
       <c r="B125" s="43" t="s">
         <v>828</v>
@@ -21497,7 +21497,7 @@
       <c r="P125" s="33"/>
       <c r="Q125" s="33"/>
     </row>
-    <row r="126" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="126" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A126" s="24"/>
       <c r="B126" s="43" t="s">
         <v>830</v>
@@ -21524,7 +21524,7 @@
       <c r="P126" s="33"/>
       <c r="Q126" s="33"/>
     </row>
-    <row r="127" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="127" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A127" s="24"/>
       <c r="B127" s="43" t="s">
         <v>832</v>
@@ -21551,7 +21551,7 @@
       <c r="P127" s="33"/>
       <c r="Q127" s="33"/>
     </row>
-    <row r="128" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="128" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A128" s="24"/>
       <c r="B128" s="43" t="s">
         <v>834</v>
@@ -21578,7 +21578,7 @@
       <c r="P128" s="33"/>
       <c r="Q128" s="33"/>
     </row>
-    <row r="129" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="129" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A129" s="24"/>
       <c r="B129" s="43" t="s">
         <v>836</v>
@@ -21605,7 +21605,7 @@
       <c r="P129" s="33"/>
       <c r="Q129" s="33"/>
     </row>
-    <row r="130" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="130" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A130" s="24"/>
       <c r="B130" s="43" t="s">
         <v>293</v>
@@ -21632,7 +21632,7 @@
       <c r="P130" s="33"/>
       <c r="Q130" s="33"/>
     </row>
-    <row r="131" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="131" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A131" s="24"/>
       <c r="B131" s="43" t="s">
         <v>838</v>
@@ -21659,7 +21659,7 @@
       <c r="P131" s="33"/>
       <c r="Q131" s="33"/>
     </row>
-    <row r="132" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="132" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A132" s="24"/>
       <c r="B132" s="43" t="s">
         <v>840</v>
@@ -21686,7 +21686,7 @@
       <c r="P132" s="33"/>
       <c r="Q132" s="33"/>
     </row>
-    <row r="133" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="133" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A133" s="24"/>
       <c r="B133" s="43" t="s">
         <v>842</v>
@@ -21713,7 +21713,7 @@
       <c r="P133" s="33"/>
       <c r="Q133" s="33"/>
     </row>
-    <row r="134" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="134" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A134" s="24"/>
       <c r="B134" s="43" t="s">
         <v>844</v>
@@ -21740,7 +21740,7 @@
       <c r="P134" s="33"/>
       <c r="Q134" s="33"/>
     </row>
-    <row r="135" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="135" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A135" s="24"/>
       <c r="B135" s="43" t="s">
         <v>846</v>
@@ -21767,7 +21767,7 @@
       <c r="P135" s="33"/>
       <c r="Q135" s="33"/>
     </row>
-    <row r="136" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="136" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A136" s="24"/>
       <c r="B136" s="43" t="s">
         <v>848</v>
@@ -21794,7 +21794,7 @@
       <c r="P136" s="33"/>
       <c r="Q136" s="33"/>
     </row>
-    <row r="137" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="137" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A137" s="24"/>
       <c r="B137" s="43" t="s">
         <v>850</v>
@@ -21821,7 +21821,7 @@
       <c r="P137" s="33"/>
       <c r="Q137" s="33"/>
     </row>
-    <row r="138" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="138" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A138" s="24"/>
       <c r="B138" s="43" t="s">
         <v>852</v>
@@ -21848,7 +21848,7 @@
       <c r="P138" s="33"/>
       <c r="Q138" s="33"/>
     </row>
-    <row r="139" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="139" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A139" s="24"/>
       <c r="B139" s="43" t="s">
         <v>854</v>
@@ -21875,7 +21875,7 @@
       <c r="P139" s="33"/>
       <c r="Q139" s="33"/>
     </row>
-    <row r="140" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="140" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A140" s="24"/>
       <c r="B140" s="43" t="s">
         <v>856</v>
@@ -21902,7 +21902,7 @@
       <c r="P140" s="33"/>
       <c r="Q140" s="33"/>
     </row>
-    <row r="141" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="141" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A141" s="24"/>
       <c r="B141" s="43" t="s">
         <v>858</v>
@@ -21929,7 +21929,7 @@
       <c r="P141" s="33"/>
       <c r="Q141" s="33"/>
     </row>
-    <row r="142" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="142" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A142" s="24"/>
       <c r="B142" s="43" t="s">
         <v>860</v>
@@ -21956,7 +21956,7 @@
       <c r="P142" s="33"/>
       <c r="Q142" s="33"/>
     </row>
-    <row r="143" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="143" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A143" s="24"/>
       <c r="B143" s="43" t="s">
         <v>862</v>
@@ -21983,7 +21983,7 @@
       <c r="P143" s="33"/>
       <c r="Q143" s="33"/>
     </row>
-    <row r="144" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="144" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A144" s="24"/>
       <c r="B144" s="43" t="s">
         <v>864</v>
@@ -22010,7 +22010,7 @@
       <c r="P144" s="33"/>
       <c r="Q144" s="33"/>
     </row>
-    <row r="145" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="145" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A145" s="24"/>
       <c r="B145" s="36" t="s">
         <v>866</v>
@@ -22037,7 +22037,7 @@
       <c r="P145" s="33"/>
       <c r="Q145" s="33"/>
     </row>
-    <row r="146" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="146" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A146" s="24"/>
       <c r="B146" s="43" t="s">
         <v>868</v>
@@ -22095,7 +22095,7 @@
       <c r="P147" s="33"/>
       <c r="Q147" s="33"/>
     </row>
-    <row r="148" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="148" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A148" s="24"/>
       <c r="B148" s="43" t="s">
         <v>873</v>
@@ -22184,7 +22184,7 @@
       <c r="P150" s="33"/>
       <c r="Q150" s="33"/>
     </row>
-    <row r="151" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="151" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A151" s="24"/>
       <c r="B151" s="43" t="s">
         <v>881</v>
@@ -22211,7 +22211,7 @@
       <c r="P151" s="33"/>
       <c r="Q151" s="33"/>
     </row>
-    <row r="152" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="152" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A152" s="24"/>
       <c r="B152" s="43" t="s">
         <v>883</v>
@@ -22238,7 +22238,7 @@
       <c r="P152" s="33"/>
       <c r="Q152" s="33"/>
     </row>
-    <row r="153" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="153" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A153" s="24"/>
       <c r="B153" s="43" t="s">
         <v>885</v>
@@ -22265,7 +22265,7 @@
       <c r="P153" s="33"/>
       <c r="Q153" s="33"/>
     </row>
-    <row r="154" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="154" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A154" s="24"/>
       <c r="B154" s="43" t="s">
         <v>887</v>
@@ -22292,7 +22292,7 @@
       <c r="P154" s="33"/>
       <c r="Q154" s="33"/>
     </row>
-    <row r="155" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="155" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A155" s="24"/>
       <c r="B155" s="43" t="s">
         <v>889</v>
@@ -22319,7 +22319,7 @@
       <c r="P155" s="33"/>
       <c r="Q155" s="33"/>
     </row>
-    <row r="156" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="156" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A156" s="24"/>
       <c r="B156" s="43" t="s">
         <v>891</v>
@@ -22346,7 +22346,7 @@
       <c r="P156" s="33"/>
       <c r="Q156" s="33"/>
     </row>
-    <row r="157" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="157" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A157" s="24"/>
       <c r="B157" s="43" t="s">
         <v>893</v>
@@ -22373,7 +22373,7 @@
       <c r="P157" s="33"/>
       <c r="Q157" s="33"/>
     </row>
-    <row r="158" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="158" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A158" s="24"/>
       <c r="B158" s="43" t="s">
         <v>267</v>
@@ -22400,7 +22400,7 @@
       <c r="P158" s="33"/>
       <c r="Q158" s="33"/>
     </row>
-    <row r="159" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="159" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A159" s="24"/>
       <c r="B159" s="43" t="s">
         <v>895</v>
@@ -22427,7 +22427,7 @@
       <c r="P159" s="33"/>
       <c r="Q159" s="33"/>
     </row>
-    <row r="160" s="5" customFormat="1" ht="13.95" hidden="1" customHeight="1" spans="1:17">
+    <row r="160" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A160" s="24"/>
       <c r="B160" s="43" t="s">
         <v>897</v>
@@ -23880,11 +23880,6 @@
     <row r="284" ht="13.95" customHeight="1"/>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A5:Q160" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Y"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <mergeCells count="19">
